--- a/FILES/VENTE_PAR_CATEGORIE/category-sales-summary-2026-10-02-2026-10-02.xlsx
+++ b/FILES/VENTE_PAR_CATEGORIE/category-sales-summary-2026-10-02-2026-10-02.xlsx
@@ -5,30 +5,17 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\FANOMEZANA\SUIVI SERVICE\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\FANOMEZANA\PROJETS\NOUVEAUX_RECAP\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F6C047F2-ED90-417B-87BC-05EE89E349BA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{84F9C9E3-C9F6-4D46-89CA-7100454FEEEC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="19440" windowHeight="14880" xr2:uid="{A5629E8F-0848-4232-8B71-03898736F0A3}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="19440" windowHeight="14880" xr2:uid="{BDE2D670-B46D-43B2-9510-F120C1C35EB3}"/>
   </bookViews>
   <sheets>
-    <sheet name="feuille1" sheetId="1" r:id="rId1"/>
+    <sheet name="category-sales-summary-2026-10-" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="191029"/>
-  <extLst>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
-      </xcalcf:calcFeatures>
-    </ext>
-  </extLst>
+  <calcPr calcId="0"/>
 </workbook>
 </file>
 
@@ -977,12 +964,9 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C147F678-8C1A-4A5D-B5B3-FDF32D9ACC54}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{81395B86-1ADA-4512-BB5E-E162522AEBFE}">
   <dimension ref="A1:K9"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <cols>
-    <col min="1" max="1" width="20.28515625" customWidth="1"/>
-  </cols>
   <sheetData>
     <row r="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
